--- a/grupos/3APM - Estadisticos 20241.xlsx
+++ b/grupos/3APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -182,27 +182,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Faltante Faltante Faltante</t>
+    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -278,9 +278,6 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
@@ -302,9 +299,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -362,9 +356,6 @@
     <t>JUAN PABLO</t>
   </si>
   <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
     <t>JOSELYN</t>
   </si>
   <si>
@@ -411,9 +402,6 @@
   </si>
   <si>
     <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
   </si>
 </sst>
 </file>
@@ -953,34 +941,34 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1010,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -1019,13 +1007,13 @@
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE4">
         <v>9</v>
       </c>
       <c r="AF4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>-1</v>
@@ -1054,34 +1042,34 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1126,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="AF5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>-1</v>
@@ -1155,34 +1143,34 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1227,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="AF6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>-1</v>
@@ -1256,34 +1244,34 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1313,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>10</v>
@@ -1322,13 +1310,13 @@
         <v>8</v>
       </c>
       <c r="AD7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>-1</v>
@@ -1357,34 +1345,34 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1411,10 +1399,10 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1423,13 +1411,13 @@
         <v>10</v>
       </c>
       <c r="AD8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>-1</v>
@@ -1458,34 +1446,34 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1515,10 +1503,10 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1527,10 +1515,10 @@
         <v>10</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>-1</v>
@@ -1559,34 +1547,34 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1616,10 +1604,10 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1631,7 +1619,7 @@
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>-1</v>
@@ -1660,34 +1648,34 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1726,13 +1714,13 @@
         <v>10</v>
       </c>
       <c r="AD11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>-1</v>
@@ -1761,34 +1749,34 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1815,25 +1803,25 @@
         <v>-1</v>
       </c>
       <c r="Z12">
+        <v>7</v>
+      </c>
+      <c r="AA12">
+        <v>8</v>
+      </c>
+      <c r="AB12">
+        <v>9</v>
+      </c>
+      <c r="AC12">
+        <v>8</v>
+      </c>
+      <c r="AD12">
+        <v>9</v>
+      </c>
+      <c r="AE12">
         <v>6</v>
       </c>
-      <c r="AA12">
-        <v>8</v>
-      </c>
-      <c r="AB12">
-        <v>9</v>
-      </c>
-      <c r="AC12">
-        <v>8</v>
-      </c>
-      <c r="AD12">
-        <v>9</v>
-      </c>
-      <c r="AE12">
-        <v>7</v>
-      </c>
       <c r="AF12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>-1</v>
@@ -1862,34 +1850,34 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1916,13 +1904,13 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -1934,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG13">
         <v>-1</v>
@@ -1963,34 +1951,34 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -2023,7 +2011,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -2035,7 +2023,7 @@
         <v>5</v>
       </c>
       <c r="AF14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AG14">
         <v>-1</v>
@@ -2064,34 +2052,34 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2124,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -2136,7 +2124,7 @@
         <v>7</v>
       </c>
       <c r="AF15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG15">
         <v>-1</v>
@@ -2165,34 +2153,34 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2222,10 +2210,10 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>9</v>
@@ -2234,10 +2222,10 @@
         <v>7</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AG16">
         <v>-1</v>
@@ -2266,34 +2254,34 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2326,7 +2314,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2338,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="AF17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>-1</v>
@@ -2367,34 +2355,34 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2421,13 +2409,13 @@
         <v>-1</v>
       </c>
       <c r="Z18">
+        <v>7</v>
+      </c>
+      <c r="AA18">
         <v>6</v>
       </c>
-      <c r="AA18">
-        <v>5</v>
-      </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2439,7 +2427,7 @@
         <v>6</v>
       </c>
       <c r="AF18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2468,34 +2456,34 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2540,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="AF19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>-1</v>
@@ -2569,34 +2557,34 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2623,13 +2611,13 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2638,10 +2626,10 @@
         <v>9</v>
       </c>
       <c r="AE20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>-1</v>
@@ -2670,34 +2658,34 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2730,19 +2718,19 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE21">
         <v>7</v>
       </c>
       <c r="AF21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>-1</v>
@@ -2771,34 +2759,34 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2831,7 +2819,7 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2840,10 +2828,10 @@
         <v>10</v>
       </c>
       <c r="AE22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>-1</v>
@@ -2872,34 +2860,34 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2932,19 +2920,19 @@
         <v>10</v>
       </c>
       <c r="AB23">
+        <v>8</v>
+      </c>
+      <c r="AC23">
+        <v>9</v>
+      </c>
+      <c r="AD23">
+        <v>9</v>
+      </c>
+      <c r="AE23">
         <v>7</v>
       </c>
-      <c r="AC23">
-        <v>9</v>
-      </c>
-      <c r="AD23">
-        <v>9</v>
-      </c>
-      <c r="AE23">
-        <v>6</v>
-      </c>
       <c r="AF23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG23">
         <v>-1</v>
@@ -2973,34 +2961,34 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -3030,10 +3018,10 @@
         <v>9</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -3045,7 +3033,7 @@
         <v>10</v>
       </c>
       <c r="AF24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG24">
         <v>-1</v>
@@ -3074,34 +3062,34 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3131,10 +3119,10 @@
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -3146,7 +3134,7 @@
         <v>10</v>
       </c>
       <c r="AF25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>-1</v>
@@ -3175,34 +3163,34 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3247,7 +3235,7 @@
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>-1</v>
@@ -3276,34 +3264,34 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3333,7 +3321,7 @@
         <v>9</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -3342,13 +3330,13 @@
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>-1</v>
@@ -3377,34 +3365,34 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3449,7 +3437,7 @@
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>-1</v>
@@ -3478,34 +3466,34 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3538,19 +3526,19 @@
         <v>7</v>
       </c>
       <c r="AB29">
+        <v>8</v>
+      </c>
+      <c r="AC29">
+        <v>8</v>
+      </c>
+      <c r="AD29">
+        <v>10</v>
+      </c>
+      <c r="AE29">
         <v>7</v>
       </c>
-      <c r="AC29">
-        <v>8</v>
-      </c>
-      <c r="AD29">
-        <v>10</v>
-      </c>
-      <c r="AE29">
-        <v>8</v>
-      </c>
       <c r="AF29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>-1</v>
@@ -3579,34 +3567,34 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3648,10 +3636,10 @@
         <v>10</v>
       </c>
       <c r="AE30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AG30">
         <v>-1</v>
@@ -3680,34 +3668,34 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3734,13 +3722,13 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3752,7 +3740,7 @@
         <v>5</v>
       </c>
       <c r="AF31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AG31">
         <v>-1</v>
@@ -3915,7 +3903,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3939,7 +3927,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3963,7 +3951,7 @@
         <v>100</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -3992,7 +3980,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -4016,7 +4004,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4040,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -4069,7 +4057,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -4093,7 +4081,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4117,7 +4105,7 @@
         <v>100</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -4146,7 +4134,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -4170,7 +4158,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4194,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -4223,7 +4211,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -4232,7 +4220,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4247,7 +4235,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4256,7 +4244,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4271,7 +4259,7 @@
         <v>100</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -4300,13 +4288,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -4321,16 +4309,16 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4345,10 +4333,10 @@
         <v>100</v>
       </c>
       <c r="W9">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -4377,7 +4365,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4401,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4425,7 +4413,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -4454,13 +4442,13 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -4478,13 +4466,13 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4502,7 +4490,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -4531,7 +4519,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4552,10 +4540,10 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4576,10 +4564,10 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -4608,7 +4596,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4632,7 +4620,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4656,7 +4644,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -4685,16 +4673,16 @@
         <v>83.3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>90</v>
+        <v>57.5</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4703,22 +4691,22 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O14">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>57.5</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -4727,13 +4715,13 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="W14">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -4762,7 +4750,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -4786,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4810,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -4839,7 +4827,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4848,7 +4836,7 @@
         <v>95</v>
       </c>
       <c r="K16">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4857,13 +4845,13 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4872,7 +4860,7 @@
         <v>95</v>
       </c>
       <c r="S16">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4881,13 +4869,13 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="W16">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -4916,7 +4904,7 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -4940,7 +4928,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4964,7 +4952,7 @@
         <v>100</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -4993,7 +4981,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -5014,10 +5002,10 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5038,10 +5026,10 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -5070,7 +5058,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -5091,10 +5079,10 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5115,10 +5103,10 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -5147,7 +5135,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -5171,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5195,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -5224,7 +5212,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -5245,10 +5233,10 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5269,10 +5257,10 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -5301,7 +5289,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -5310,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>97.8</v>
+        <v>96.7</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5322,10 +5310,10 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5334,7 +5322,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>97.8</v>
+        <v>96.7</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -5346,10 +5334,10 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -5378,13 +5366,13 @@
         <v>83.3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -5399,16 +5387,16 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5423,10 +5411,10 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -5455,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -5464,7 +5452,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5479,7 +5467,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5488,7 +5476,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5503,7 +5491,7 @@
         <v>100</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -5532,7 +5520,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -5556,7 +5544,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5580,7 +5568,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -5609,7 +5597,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -5633,7 +5621,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5657,7 +5645,7 @@
         <v>100</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -5686,7 +5674,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -5695,7 +5683,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5710,7 +5698,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5719,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -5734,7 +5722,7 @@
         <v>100</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y27">
         <v>100</v>
@@ -5763,7 +5751,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -5787,7 +5775,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5811,7 +5799,7 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -5840,7 +5828,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -5849,7 +5837,7 @@
         <v>95</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5861,10 +5849,10 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5873,7 +5861,7 @@
         <v>95</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5885,10 +5873,10 @@
         <v>100</v>
       </c>
       <c r="W29">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -5917,13 +5905,13 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5941,13 +5929,13 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5965,7 +5953,7 @@
         <v>100</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y30">
         <v>100</v>
@@ -5994,16 +5982,16 @@
         <v>88.90000000000001</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K31">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -6012,22 +6000,22 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="O31">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>80.5</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S31">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6036,13 +6024,13 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="W31">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>80.5</v>
       </c>
       <c r="Y31">
         <v>100</v>
@@ -6102,7 +6090,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -6131,7 +6119,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -6140,27 +6128,30 @@
         <v>28</v>
       </c>
       <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="H3">
+        <v>9.1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3" s="2">
         <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>28</v>
-      </c>
-      <c r="J3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -6169,19 +6160,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6192,7 +6183,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -6213,7 +6204,7 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6224,7 +6215,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -6233,19 +6224,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6256,7 +6247,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -6277,7 +6268,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6288,7 +6279,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -6309,7 +6300,7 @@
         <v>3.6</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6329,19 +6320,19 @@
         <v>28</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6357,7 +6348,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6384,566 +6375,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920151</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920152</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920153</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920155</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920154</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920325</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920250</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920157</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920158</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920159</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920160</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920161</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920162</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920163</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920164</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920297</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920165</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920166</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920167</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920310</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920169</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920354</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920170</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920173</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920172</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920311</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920174</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920313</v>
-      </c>
-      <c r="B29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6951,7 +6382,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6989,13 +6420,13 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -7006,22 +6437,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920151</v>
+        <v>23330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -7029,19 +6460,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920152</v>
+        <v>23330051920153</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -7052,13 +6483,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920152</v>
+        <v>23330051920155</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
         <v>105</v>
@@ -7067,7 +6498,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -7075,10 +6506,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920153</v>
+        <v>23330051920154</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
         <v>89</v>
@@ -7087,7 +6518,7 @@
         <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
@@ -7098,22 +6529,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920153</v>
+        <v>23330051920325</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -7121,19 +6552,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920155</v>
+        <v>23330051920250</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>54</v>
@@ -7144,22 +6575,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920155</v>
+        <v>23330051920157</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -7167,19 +6598,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920154</v>
+        <v>23330051920158</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -7190,22 +6621,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920154</v>
+        <v>23330051920159</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -7213,19 +6644,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920325</v>
+        <v>23330051920161</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -7236,22 +6667,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920325</v>
+        <v>23330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -7259,19 +6690,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920250</v>
+        <v>23330051920163</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -7282,22 +6713,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920250</v>
+        <v>23330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -7305,19 +6736,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920157</v>
+        <v>23330051920297</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
@@ -7328,22 +6759,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920157</v>
+        <v>23330051920165</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -7351,19 +6782,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920158</v>
+        <v>23330051920166</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
         <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
@@ -7374,22 +6805,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920158</v>
+        <v>23330051920167</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -7397,19 +6828,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920159</v>
+        <v>23330051920310</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -7420,22 +6851,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920159</v>
+        <v>23330051920169</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -7443,19 +6874,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920161</v>
+        <v>23330051920354</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
@@ -7466,22 +6897,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920161</v>
+        <v>23330051920170</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -7489,19 +6920,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920162</v>
+        <v>23330051920173</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
         <v>54</v>
@@ -7512,22 +6943,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920162</v>
+        <v>23330051920172</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
         <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -7535,19 +6966,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920163</v>
+        <v>23330051920311</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
         <v>54</v>
@@ -7558,576 +6989,24 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920163</v>
+        <v>23330051920174</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920297</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920297</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920165</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920165</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920166</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920166</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920167</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>93</v>
-      </c>
-      <c r="D34" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920167</v>
-      </c>
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>23330051920310</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>23330051920310</v>
-      </c>
-      <c r="B37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>55</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>23330051920169</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>23330051920169</v>
-      </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>23330051920354</v>
-      </c>
-      <c r="B40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>23330051920354</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" t="s">
-        <v>55</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>23330051920170</v>
-      </c>
-      <c r="B42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C42" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>23330051920170</v>
-      </c>
-      <c r="B43" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>23330051920173</v>
-      </c>
-      <c r="B44" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>23330051920173</v>
-      </c>
-      <c r="B45" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>23330051920172</v>
-      </c>
-      <c r="B46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>23330051920172</v>
-      </c>
-      <c r="B47" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>23330051920311</v>
-      </c>
-      <c r="B48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>23330051920311</v>
-      </c>
-      <c r="B49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" t="s">
-        <v>70</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" t="s">
-        <v>55</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>23330051920174</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>23330051920174</v>
-      </c>
-      <c r="B51" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" t="s">
-        <v>130</v>
-      </c>
-      <c r="E51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" t="s">
-        <v>55</v>
-      </c>
-      <c r="G51">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20241.xlsx
+++ b/grupos/3APM - Estadisticos 20241.xlsx
@@ -194,7 +194,7 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
+    <t>Martínez Marañon Mauricio</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
@@ -956,7 +956,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>10</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD4">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>10</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>10</v>
@@ -1259,7 +1259,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>9</v>
@@ -1307,7 +1307,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>8</v>
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>10</v>
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>9</v>
@@ -1562,7 +1562,7 @@
         <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>10</v>
@@ -1663,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>10</v>
@@ -1764,7 +1764,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>9</v>
@@ -1812,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD12">
         <v>9</v>
@@ -1865,7 +1865,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>10</v>
@@ -1966,7 +1966,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -2014,7 +2014,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD14">
         <v>5</v>
@@ -2067,7 +2067,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>10</v>
@@ -2115,7 +2115,7 @@
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>10</v>
@@ -2168,7 +2168,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>6</v>
@@ -2269,7 +2269,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>10</v>
@@ -2317,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD17">
         <v>10</v>
@@ -2370,7 +2370,7 @@
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>8</v>
@@ -2418,7 +2418,7 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>9</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>10</v>
@@ -2572,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>8</v>
@@ -2620,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD20">
         <v>9</v>
@@ -2673,7 +2673,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>8</v>
@@ -2721,7 +2721,7 @@
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD21">
         <v>9</v>
@@ -2774,7 +2774,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>10</v>
@@ -2822,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>10</v>
@@ -2875,7 +2875,7 @@
         <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>9</v>
@@ -2923,7 +2923,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>9</v>
@@ -2976,7 +2976,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>10</v>
@@ -3024,7 +3024,7 @@
         <v>9</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD24">
         <v>10</v>
@@ -3077,7 +3077,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>10</v>
@@ -3178,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>10</v>
@@ -3279,7 +3279,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>10</v>
@@ -3380,7 +3380,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>10</v>
@@ -3481,7 +3481,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>10</v>
@@ -3529,7 +3529,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD29">
         <v>10</v>
@@ -3582,7 +3582,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>10</v>
@@ -3630,7 +3630,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD30">
         <v>10</v>
@@ -3683,7 +3683,7 @@
         <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>6</v>
@@ -3731,7 +3731,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD31">
         <v>6</v>
@@ -4688,7 +4688,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N14">
         <v>50</v>
@@ -4712,7 +4712,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="V14">
         <v>50</v>
@@ -6236,7 +6236,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/3APM - Estadisticos 20241.xlsx
+++ b/grupos/3APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
   </si>
 </sst>
 </file>
@@ -5571,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5601,6 +5607,75 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920313</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920313</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3APM - Estadisticos 20241.xlsx
+++ b/grupos/3APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -182,13 +182,13 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Martínez Marañon Mauricio</t>
@@ -769,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -778,16 +778,16 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -867,19 +867,19 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -947,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -956,19 +956,19 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1036,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1045,19 +1045,19 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1066,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1134,16 +1134,16 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1214,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1223,16 +1223,16 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1303,7 +1303,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1312,16 +1312,16 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1392,7 +1392,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1401,19 +1401,19 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1425,13 +1425,13 @@
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1481,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1490,16 +1490,16 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1514,13 +1514,13 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1570,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1579,16 +1579,16 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1609,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1659,7 +1659,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1668,16 +1668,16 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1748,7 +1748,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1757,16 +1757,16 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1837,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1846,16 +1846,16 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1926,7 +1926,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1935,16 +1935,16 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1959,7 +1959,7 @@
         <v>9</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2015,7 +2015,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2024,19 +2024,19 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2104,7 +2104,7 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2113,16 +2113,16 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2193,7 +2193,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2202,16 +2202,16 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2282,7 +2282,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2291,16 +2291,16 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2312,7 +2312,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2371,7 +2371,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2380,16 +2380,16 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2401,7 +2401,7 @@
         <v>9</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2460,7 +2460,7 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2469,19 +2469,19 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2490,7 +2490,7 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2499,7 +2499,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2549,7 +2549,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2558,19 +2558,19 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2638,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2647,16 +2647,16 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2727,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2736,19 +2736,19 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2816,7 +2816,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2825,16 +2825,16 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2905,7 +2905,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2914,16 +2914,16 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2994,7 +2994,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3003,19 +3003,19 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3083,7 +3083,7 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3092,19 +3092,19 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3116,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>7</v>
@@ -3172,7 +3172,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3181,16 +3181,16 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3211,7 +3211,7 @@
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3723,7 +3723,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3859,7 +3859,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3927,7 +3927,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4063,7 +4063,7 @@
         <v>41.5</v>
       </c>
       <c r="P14">
-        <v>57.5</v>
+        <v>35.9</v>
       </c>
       <c r="Q14">
         <v>50</v>
@@ -4072,16 +4072,16 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T14">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="U14">
         <v>45.5</v>
       </c>
       <c r="V14">
-        <v>41.5</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4199,7 +4199,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
         <v>94.40000000000001</v>
@@ -4211,7 +4211,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U16">
         <v>97</v>
@@ -4335,7 +4335,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4539,7 +4539,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4607,7 +4607,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
         <v>96.7</v>
@@ -4675,7 +4675,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4743,7 +4743,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="Q24">
         <v>97.8</v>
@@ -5083,7 +5083,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="Q29">
         <v>98.90000000000001</v>
@@ -5151,7 +5151,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5219,7 +5219,7 @@
         <v>80.5</v>
       </c>
       <c r="P31">
-        <v>97.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="Q31">
         <v>94.40000000000001</v>
@@ -5231,13 +5231,13 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U31">
         <v>84.8</v>
       </c>
       <c r="V31">
-        <v>80.5</v>
+        <v>87.3</v>
       </c>
     </row>
   </sheetData>
@@ -5294,7 +5294,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -5315,7 +5315,7 @@
         <v>7.1</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5347,7 +5347,7 @@
         <v>7.1</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5367,19 +5367,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5411,7 +5411,7 @@
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5577,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5624,7 +5624,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5647,32 +5647,9 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920313</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20241.xlsx
+++ b/grupos/3APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -182,16 +182,16 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Martínez Marañon Mauricio</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
@@ -784,7 +784,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -873,7 +873,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1051,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1072,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1140,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1161,7 +1161,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1407,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1496,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1517,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -1585,7 +1585,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1674,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1763,7 +1763,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1784,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -1852,7 +1852,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -1873,7 +1873,7 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -1941,7 +1941,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2030,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2051,7 +2051,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2119,7 +2119,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2208,7 +2208,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2297,7 +2297,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2318,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2386,7 +2386,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2407,7 +2407,7 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2496,7 +2496,7 @@
         <v>9</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2564,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2653,7 +2653,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2742,7 +2742,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2831,7 +2831,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2920,7 +2920,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3187,7 +3187,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3208,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>6</v>
@@ -3398,7 +3398,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3466,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3602,7 +3602,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3670,7 +3670,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3738,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3942,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>93.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4078,7 +4078,7 @@
         <v>33.3</v>
       </c>
       <c r="U14">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="V14">
         <v>61.9</v>
@@ -4214,7 +4214,7 @@
         <v>91.7</v>
       </c>
       <c r="U16">
-        <v>97</v>
+        <v>93.8</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4282,7 +4282,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4350,7 +4350,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4418,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4554,7 +4554,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4622,7 +4622,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>84.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4690,7 +4690,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>81.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5098,7 +5098,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5166,7 +5166,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5234,7 +5234,7 @@
         <v>91.7</v>
       </c>
       <c r="U31">
-        <v>84.8</v>
+        <v>87.5</v>
       </c>
       <c r="V31">
         <v>87.3</v>
@@ -5294,7 +5294,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -5315,7 +5315,7 @@
         <v>7.1</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5335,19 +5335,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5379,7 +5379,7 @@
         <v>3.6</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5390,7 +5390,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5411,7 +5411,7 @@
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5577,7 +5577,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5624,32 +5624,9 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920313</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20241.xlsx
+++ b/grupos/3APM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -182,24 +182,24 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Martínez Marañon Mauricio</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -216,12 +216,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
   </si>
 </sst>
 </file>
@@ -772,10 +766,10 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>9</v>
@@ -861,10 +855,10 @@
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -950,10 +944,10 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -1039,10 +1033,10 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1128,10 +1122,10 @@
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1217,10 +1211,10 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1306,10 +1300,10 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1395,10 +1389,10 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1484,10 +1478,10 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>9</v>
@@ -1505,10 +1499,10 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1573,10 +1567,10 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1662,10 +1656,10 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -1751,10 +1745,10 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -1772,10 +1766,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>10</v>
@@ -1840,10 +1834,10 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -1929,10 +1923,10 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -2018,10 +2012,10 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -2039,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2107,10 +2101,10 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -2196,10 +2190,10 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -2285,10 +2279,10 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2309,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>9</v>
@@ -2374,10 +2368,10 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -2463,10 +2457,10 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -2484,7 +2478,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2552,10 +2546,10 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2641,10 +2635,10 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2730,10 +2724,10 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -2751,7 +2745,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2819,10 +2813,10 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -2908,10 +2902,10 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>10</v>
@@ -2997,10 +2991,10 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>9</v>
@@ -3086,10 +3080,10 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -3107,7 +3101,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3175,10 +3169,10 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -3196,10 +3190,10 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3658,7 +3652,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3726,7 +3720,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3930,7 +3924,7 @@
         <v>95.3</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4066,7 +4060,7 @@
         <v>35.9</v>
       </c>
       <c r="Q14">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4202,7 +4196,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q16">
-        <v>94.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4610,7 +4604,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q22">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4746,7 +4740,7 @@
         <v>99.2</v>
       </c>
       <c r="Q24">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4950,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5086,7 +5080,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="Q29">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5222,10 +5216,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="Q31">
-        <v>94.40000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5294,7 +5288,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -5303,19 +5297,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5326,7 +5320,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5347,7 +5341,7 @@
         <v>3.6</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5358,7 +5352,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5379,7 +5373,7 @@
         <v>3.6</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5390,7 +5384,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5411,7 +5405,7 @@
         <v>3.6</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5422,7 +5416,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5443,7 +5437,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5454,7 +5448,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5475,7 +5469,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5577,7 +5571,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5607,29 +5601,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920313</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
